--- a/修正履歴.xlsx
+++ b/修正履歴.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{D598A26E-3CE0-478B-8CBA-B84AEA3FEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{948F8AC3-E8B2-4BD9-97BF-ECDD0D7C3CC9}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{D598A26E-3CE0-478B-8CBA-B84AEA3FEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D985A08C-9252-4E5E-A9E2-632AD88DB2FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
     <sheet name="No1" sheetId="2" r:id="rId2"/>
     <sheet name="No2" sheetId="3" r:id="rId3"/>
+    <sheet name="No3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="282">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -832,6 +833,1031 @@
       </rPr>
       <t>レポートで以下を確認:</t>
     </r>
+  </si>
+  <si>
+    <t># SP0557 RTL最適化 変更履歴</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>## 変更一覧</t>
+  </si>
+  <si>
+    <t>### 変更1: ppmc_phgen インスタンス削除</t>
+  </si>
+  <si>
+    <t>| 項目 | 内容 |</t>
+  </si>
+  <si>
+    <t>|------|------|</t>
+  </si>
+  <si>
+    <t>### 変更2: ppmc_enblr_S118M デッドコード削除</t>
+  </si>
+  <si>
+    <t>### 変更3: adc_reg.vhd 未使用チャネル削除</t>
+  </si>
+  <si>
+    <t>### 変更4: GPIO未使用出力レジスタ削除</t>
+  </si>
+  <si>
+    <t>### 変更5: ppmc_rgstr.vhd 冗長な自己代入削除</t>
+  </si>
+  <si>
+    <t>## 未実施の候補（コメントとして記載）</t>
+  </si>
+  <si>
+    <t>### 候補6: gpio02 未使用入力レジスタ簡素化</t>
+  </si>
+  <si>
+    <t>### 候補7: cds.vhd azレジスタ幅削減</t>
+  </si>
+  <si>
+    <t>azは10ビットだが判定ロジックではaz(0)-az(4)のみ使用。az(5)-az(9)はアイドル検出比較のみに関与。</t>
+  </si>
+  <si>
+    <t>## 削減効果の試算まとめ</t>
+  </si>
+  <si>
+    <t>| # | 変更対象 | 変更種別 | FF削減 | LUT削減 | 推定SLICE削減 |</t>
+  </si>
+  <si>
+    <t>|---|---------|---------|--------|---------|-------------|</t>
+  </si>
+  <si>
+    <t>| 1 | ppmc_phgen | デッド回路削除 | 156 | 260 | ~100 |</t>
+  </si>
+  <si>
+    <t>| 2 | ppmc_enblr | デッドコード削除 | 130 | 195 | ~70 |</t>
+  </si>
+  <si>
+    <t>| 3 | adc_reg | 未使用チャネル | 72 | 40 | ~36 |</t>
+  </si>
+  <si>
+    <t>| 4 | gpio_op_reg | 未使用出力 | 384 | 48 | ~100 |</t>
+  </si>
+  <si>
+    <t>| 5 | ppmc_rgstr | 自己代入削除 | 0 | 20 | ~10 |</t>
+  </si>
+  <si>
+    <t>## 変更ファイル一覧</t>
+  </si>
+  <si>
+    <t>| ファイル | 変更内容 |</t>
+  </si>
+  <si>
+    <t>|---------|---------|</t>
+  </si>
+  <si>
+    <t>## ポートインターフェース変更</t>
+  </si>
+  <si>
+    <t>- `ppmc_reg_S118M.vhd`:</t>
+  </si>
+  <si>
+    <t>  - ppmc_phgenコンポーネント宣言をコメントアウト</t>
+  </si>
+  <si>
+    <t>  - ppmc_phgenインスタンス（inst_ppmc_phgen）を削除</t>
+  </si>
+  <si>
+    <t>  - S1/S2/S3/S4出力を`'0'`に固定</t>
+  </si>
+  <si>
+    <t>- `ppmc_top_S118M.vhd`:</t>
+  </si>
+  <si>
+    <t>  - s_S1〜s_S4信号宣言をコメントアウト</t>
+  </si>
+  <si>
+    <t>  - ANDゲート（S1-S4 = s_S1-s_S4 AND s_ENB）を削除</t>
+  </si>
+  <si>
+    <t>  - S1-S4出力を直接`'0'`に固定</t>
+  </si>
+  <si>
+    <t>  - ppmc_reg_S118Mポートマップ：S1-S4を`open`に変更</t>
+  </si>
+  <si>
+    <t>- `dsb_wait_cnt`（8ビットカウンタ）、`s_PLUSE10M_ST`、`st_stop_old`信号宣言を削除</t>
+  </si>
+  <si>
+    <t>- P_STOPエッジハンドラを単一分岐に簡略化（if/elseの両分岐が同一だった）</t>
+  </si>
+  <si>
+    <t>- ダウンタイマーブランチを完全削除</t>
+  </si>
+  <si>
+    <t>- `s_P_STOP_old`をリセットリストに追加（元コードで欠落していた修正）</t>
+  </si>
+  <si>
+    <t>- CURRENT_DOWNポートは維持し`'0'`固定を継続（上位互換性）</t>
+  </si>
+  <si>
+    <t>- s_REG3〜s_REG8の信号宣言・レジスタプロセスを削除</t>
+  </si>
+  <si>
+    <t>- s_comp信号を削除</t>
+  </si>
+  <si>
+    <t>- ADDATA03〜ADDATA08出力を`(others =&gt; '0')`に固定</t>
+  </si>
+  <si>
+    <t>- caseステートメントからCH "010"〜"111"の分岐を削除（`when others =&gt; null`に統合）</t>
+  </si>
+  <si>
+    <t>- 残るcaseステートメントの冗長な自己代入（`s_REG1 &lt;= s_REG1`等）を削除</t>
+  </si>
+  <si>
+    <t>- チャネル20〜31のgpio_op_regインスタンス（inst20〜inst31）を削除（12インスタンス × 2 GPIOモジュール = 24インスタンス分）</t>
+  </si>
+  <si>
+    <t>- GPO_20〜GPO_31出力を`(others =&gt; '0')`に固定</t>
+  </si>
+  <si>
+    <t>- 対応するgpio_ip_regインスタンス（20〜31）は全て保持（レジスタ読み出しパスに必要）</t>
+  </si>
+  <si>
+    <t>- REGDO ORチェーンは変更なし</t>
+  </si>
+  <si>
+    <t>- INIT_REG_O, COMMAND_REG_O/com_cng, PULSE_REG_O (L/H)</t>
+  </si>
+  <si>
+    <t>- HIGH_FREQ_REG_O (L/H), LOW_FREQ_REG_O (L/H)</t>
+  </si>
+  <si>
+    <t>- ACC_RATE_REG_O (L/H), SLOW_DOWN_REG_O (L/H)</t>
+  </si>
+  <si>
+    <t>- LIMIT_MASK_REG_O, PRE_REG_O, MORE_REG_O (L/H)</t>
+  </si>
+  <si>
+    <t>- DOWNDELAY_REG_O, CTRL2_REG_O, MPO_REG_A_O, MPO_REG_B_O</t>
+  </si>
+  <si>
+    <t>gpio02のGPI_15-16, GPI_18-31はoct0（定数`"00000000"`）に接続。これらのgpio_ip_regは常に'0'を格納するが、レジスタマップの一部として読み出しアクセスが可能。</t>
+  </si>
+  <si>
+    <t>| `SP0557/compactppmc/ppmc_reg_S118M.vhd` | ppmc_phgen削除、S1-S4固定 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/compactppmc/ppmc_top_S118M.vhd` | S1-S4 AND削除、出力固定 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/compactppmc/ppmc_enblr_S118M.vhd` | CURRENT_DOWNタイマー削除 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/compactppmc/ppmc_rgstr.vhd` | 冗長な自己代入削除 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/ad_ctrl/adc_reg.vhd` | 未使用CH3-8レジスタ削除 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/gpio/gpio_reg.vhd` | op_reg inst20-31削除、候補コメント追加 |</t>
+  </si>
+  <si>
+    <t>| `SP0557/slv_com/cds.vhd` | 候補コメント追加のみ |</t>
+  </si>
+  <si>
+    <r>
+      <t>**日付**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 2026-02-20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**目的**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: FPGA SLICE占有率削減（~80% → 70-75%目標）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**制約**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 機能変更なし（通信タイミング・プロトコル・レジスタマップ不変）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/compactppmc/ppmc_reg_S118M.vhd`, `SP0557/compactppmc/ppmc_top_S118M.vhd` |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**変更種別**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | デッド回路削除 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 156 FF + 260 LUT ≈ 100 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**根拠**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: SP0557.vhd において全13個のPPMCインスタンス（stm01-stm13）のS1-S4出力が全て`open`接続。ppmc_phgenは8状態FSM（STATE: 8FF + SOUT: 4FF = 12FF + ~20 LUT）を持つが、出力は最終的にどこにも接続されていないデッドロジック。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**変更内容**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**安全性**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: ppmc_phgenの入力信号（PULSE_OUT_EDGE, STOP等）は他コンポーネントと共有だが、出力はS1-S4のみでフィードバックなし。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/compactppmc/ppmc_enblr_S118M.vhd` |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**変更種別**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | デッドコード削除 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 130 FF + 195 LUT ≈ 70 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**根拠**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: CURRENT_DOWN出力は`'0'`にハードコード済み。関連するCURRENT_DOWNタイマー用信号（dsb_wait_cnt: 8FF, s_PLUSE10M_ST: 1FF, st_stop_old: 1FF）とロジックが残存していた。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**安全性**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: dsb_wait_cnt/s_PLUSE10M_STはCURRENT_DOWNタイマーとしてのみ機能。START_STOP出力パスへの影響なし（ph_flagはenb_wait_1280usとP_STOPのみで駆動）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/ad_ctrl/adc_reg.vhd` |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**変更種別**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 未使用チャネル削除 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 72 FF + 40 LUT ≈ 36 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**根拠**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: SP0557.vhd ADC_CONTインスタンスにおいてADDATA03〜ADDATA08は全て`open`接続。8チャネル中2チャネルのみ使用（圧力センサ2系統）。s_REG3〜s_REG8は各12FFの未使用レジスタ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/gpio/gpio_reg.vhd` |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**変更種別**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 未使用出力レジスタ削除 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 384 FF + 48 LUT ≈ 100 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**根拠**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: gpio01（Node 13）およびgpio02（Node 14）の両インスタンスにおいてGPO_20〜GPO_31が全て`OPEN`接続。各gpio_op_regは16FF（REG: 8FF + GPO: 8FF）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**安全性**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: gpio_op_regのGPO出力はトップレベルで未接続。レジスタへの書き込みは破棄されるが、元々出力先がないため機能影響なし。読み出しパス（gpio_ip_reg → REGDO）は維持。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/compactppmc/ppmc_rgstr.vhd` |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**変更種別**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 冗長コード削除 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 0 FF + 20 LUT ≈ 10 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**根拠**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 約18個のレジスタプロセスに不要な`else REG &lt;= REG`分岐が存在。VHDLの登録プロセスではelse分岐がない場合、レジスタは自動的に値を保持する。合成ツールは通常これを最適化するが、階層保持モードでは最適化が不十分になる可能性がある。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**変更内容**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: 以下のレジスタプロセスの冗長なelse自己代入分岐を削除:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**注意**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: LIMIT_MONITOR_REG、MPO_A_O/MPO_B_Oラッチプロセス、MPI_Rロードプロセスの自己代入は意図的に保持（これらはラッチ動作または明示的なデフォルト値指定として機能）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/gpio/gpio_reg.vhd`（コメントのみ） |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 240 FF ≈ 60 SLICE |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**不実施理由**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | レジスタマップ読み出し動作への影響が不確実 |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**対象ファイル**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | `SP0557/slv_com/cds.vhd`（コメントのみ） |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**推定削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | 5 FF + 5 LUT |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**不実施理由**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | タイミング動作の変更に該当（アイドル検出 100ns → 50ns @100MHz） |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**実施分合計**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**742**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**563**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**~316**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> |</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lattice FPGA（SLICE = 2 LUT4 + 2 FF）換算で、5000 SLICE規模のデバイスに対し約</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>**6-7%の削減**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を見込む。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**なし**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> — 全モジュールの外部ポートは不変。未使用出力は`'0'`に固定し、ポート宣言は維持。</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RTLの無駄を削除。昨日変更はなし。</t>
+    <rPh sb="4" eb="6">
+      <t>ムダ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -968,7 +1994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1059,6 +2085,12 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1074,6 +2106,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1452,8 +2488,12 @@
       <c r="D7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="26"/>
+      <c r="E7" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="8" spans="3:6" x14ac:dyDescent="0.4">
       <c r="C8" s="26"/>
@@ -2494,4 +3534,630 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E81A2F4-F9B4-404A-AE58-E34E7E0FCE12}">
+  <dimension ref="B2:B171"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" style="31"/>
+    <col min="2" max="2" width="255.625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="30" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="30" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B5" s="30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="30" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B8" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B10" s="30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B12" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B14" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B15" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B16" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B17" s="31" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B18" s="31" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B20" s="30" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B22" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B23" s="31" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B24" s="31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B25" s="31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B26" s="31" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B27" s="31" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B28" s="31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B29" s="31" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B30" s="31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" s="31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" s="30" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" s="30" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" s="31" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" s="31" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" s="31" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B45" s="30" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" s="31" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B49" s="31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B50" s="31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B51" s="31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B52" s="31" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B54" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B56" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B58" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B60" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B61" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B62" s="31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B63" s="31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B64" s="31" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B66" s="30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B68" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B69" s="31" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B70" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B71" s="31" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B72" s="31" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B73" s="31" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B75" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B77" s="30" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B79" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B80" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B81" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B82" s="31" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B83" s="31" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B85" s="30" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B87" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B88" s="31" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B89" s="31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B90" s="31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B91" s="31" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B93" s="30" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B95" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B97" s="30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B99" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B100" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B101" s="31" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B102" s="31" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B103" s="31" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B105" s="30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B107" s="30" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B108" s="31" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B109" s="31" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B110" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B111" s="31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B112" s="31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B114" s="30" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B116" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B118" s="30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B120" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B122" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B123" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B124" s="31" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B125" s="31" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B126" s="31" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B128" s="31" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B130" s="30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B132" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B133" s="31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B134" s="31" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B135" s="31" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B136" s="31" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B138" s="31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B140" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B142" s="30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B144" s="31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B145" s="31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B146" s="31" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B147" s="31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B148" s="31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B149" s="31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B150" s="31" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B151" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B153" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B155" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B157" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B159" s="31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B160" s="31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B161" s="31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B162" s="31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B163" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B164" s="31" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B165" s="31" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B166" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B167" s="31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B169" s="30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B171" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>